--- a/data_extactor/batch_10_fa/batch_0036_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0036_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنوری | گوش دادن فعال | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | نوشتن</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان نوشتاری | درک نوشتاری | دید نزدیک | نظم‌دهی اطلاعات | استدلال قیاسی | خلاقیت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | درک کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | ارتباط با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن</t>
+          <t>آزادی در تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان هنر، نمایش و موسیقی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | معلمان آموزش، پس از متوسطه | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان کودکستان، به جز آموزش استثنایی | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان پیش‌دبستانی، به جز آموزش استثنایی | معلمان مطالعات تفریحی و تناسب اندام، پس از متوسطه | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، کودکستان | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، پیش‌دبستانی | معلمان آموزش استثنایی، متوسطه | دستیاران آموزشی، پس از متوسطه | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان هنر، نمایش و موسیقی، آموزش عالی | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخنوری | تفکر انتقادی | نظارت | راهبردهای یادگیری | نوشتن | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | درک نوشتاری | بیان نوشتاری | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان</t>
+          <t>ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | مدیران آموزشی، کودکستان تا متوسطه | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان کودکستان، به جز آموزش استثنایی | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان پیش‌دبستانی، به جز آموزش استثنایی | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، کودکستان | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، پیش‌دبستانی | معلمان آموزش استثنایی، متوسطه | دستیاران آموزشی، پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدیران آموزشی، مهدکودک تا دبیرستان | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | راهبردهای یادگیری | سخنوری | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نوشتن | نظارت</t>
+          <t>درک مطلب | راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روانشناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | استدلال قیاسی | دید نزدیک | استدلال استقرایی | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | خلاقیت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>صرف زمان برای نشستن | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | ارتباط با دیگران | ایمیل | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | فشار زمانی</t>
+          <t>صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | ایمیل | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | معلمان آموزش، پس از متوسطه | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان کودکستان، به جز آموزش استثنایی | معلمان علوم ریاضی، پس از متوسطه | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، کودکستان | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، پیش‌دبستانی | معلمان آموزش استثنایی، متوسطه | دستیاران آموزشی، پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | مدرسان علوم ریاضی، پس از متوسطه | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخنوری | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نوشتن | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | ارتباطات و رسانه | روانشناسی | رایانه و الکترونیک | مدیریت و اداره</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>معلمان خودسازی | معلمان خصوصی | معلمان جایگزین، کوتاه‌مدت | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، پس از متوسطه | متخصصان آموزش و توسعه | مدیران آموزش و توسعه | هماهنگ‌کنندگان آموزشی | معلمان پس از متوسطه، سایر | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | مربیان مدیریت مزرعه و خانه | متخصصان آموزش بهداشت | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | مربیان و استعدادیاب‌ها | معلمان مطالعات تفریحی و تناسب اندام، پس از متوسطه | مدیران آموزشی، سایر | دستیاران آموزشی، سایر</t>
+          <t>معلمان خودسازی | معلمان خصوصی | معلمان جایگزین، کوتاه‌مدت | مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | متخصصان آموزش و توسعه | مدیران آموزش و توسعه | هماهنگ‌کنندگان آموزشی | اساتید پس از متوسطه، سایر موارد | معلمان دبستان، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | مربیان مدیریت مزرعه و خانه | متخصصان آموزش بهداشت | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مربیان و استعدادیاب‌ها | اساتید مطالعات تفریحی و تناسب اندام، پس از متوسطه | مدیران آموزشی، سایر | دستیاران آموزشی، سایر</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار Adlib Information Systems Adlib Archive | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Archivists' Toolkit | Archon | Corel Paint Shop Pro | نرم‌افزار پایگاه داده | DiMeMa CONTENTdm | زبان نشانه‌گذاری ابرمتن پویا DHTML | سیستم آرشیوی کدگذاری‌شده EAD | Esri ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Gallery Systems The Museum System | سیستم‌های اطلاعات جغرافیایی GIS | زبان نشانه‌گذاری ابرمتن HTML | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار Omeka | PREMIS | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار Adlib Information Systems Adlib Archive | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Archivists' Toolkit | Archon | Corel Paint Shop Pro | نرم‌افزار پایگاه داده | DiMeMa CONTENTdm | زبان نشانه‌گذاری ابرمتن پویا DHTML | سیستم آرشیو کدگذاری شده EAD | Esri ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Gallery Systems The Museum System | سیستم‌های سیستم اطلاعات جغرافیایی GIS | زبان نشانه‌گذاری ابرمتن HTML | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار Omeka | PREMIS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | سخنوری | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک نوشتاری | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | بیان نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها</t>
+          <t>درک کتبی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | ارتباط با دیگران | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | اهمیت تکرار کارهای مشابه</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | ارتباط با دیگران | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | کارمندان مکاتبات | موزه‌داران | تحلیلگران جرم‌شناسی دیجیتال | متخصصان مدیریت اسناد | ویراستاران | کارمندان بایگانی | متخصصان فناوری اطلاعات سلامت و مسئولان ثبت پزشکی | مورخان | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | معلمان علوم کتابداری، پس از متوسطه | تکنسین‌های کتابخانه | موزه‌داران و محافظان موزه | کارمندان اداری، عمومی | نمونه‌خوان‌ها و علامت‌گذاران کپی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | دستیاران آماری</t>
+          <t>مردم‌شناسان و باستان‌شناسان | کارمندان مکاتبات | موزه‌داران | تحلیل‌گران جرم‌شناسی دیجیتال | متخصصان مدیریت اسناد | ویراستاران | کارمندان بایگانی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مورخان | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | مدرسان علوم کتابداری، آموزش عالی | تکنسین‌های کتابخانه | تکنسین‌ها و محافظان موزه | کارمندان دفتری عمومی | مصححان و نشانه‌گذاران کپی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخنوری | درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | دید نزدیک | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | خلاقیت | نظم‌دهی اطلاعات | روانی ایده‌ها | تجسم | دید دور | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص رنگ بصری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | اصالت | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تجسم | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نتایج کاری و خروجی‌های سایر کارکنان | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | معلمان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | معلمان معماری، پس از متوسطه | آرشیوچی‌ها | معلمان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدیران هنری | معلمان هنر، نمایش و موسیقی، پس از متوسطه | معلمان زبان و ادبیات انگلیسی، پس از متوسطه | معلمان جغرافیا، پس از متوسطه | مورخان | معلمان تاریخ، پس از متوسطه | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | معلمان علوم کتابداری، پس از متوسطه | تکنسین‌های کتابخانه | موزه‌داران و محافظان موزه | طراحان صحنه و نمایشگاه | دستیاران پژوهشی علوم اجتماعی | راهنمایان تور و همراهان</t>
+          <t>مردم‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان معماری، پس از متوسطه | آرشیوچی‌ها | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | مدیران هنری | مدرسان هنر، نمایش و موسیقی، آموزش عالی | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | استادان جغرافیا، پس از متوسطه | مورخان | مدرسان تاریخ، آموزش عالی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | مدرسان علوم کتابداری، آموزش عالی | تکنسین‌های کتابخانه | تکنسین‌ها و محافظان موزه | طراحان صحنه و نمایشگاه | دستیاران تحقیقات علوم اجتماعی | راهنمایان تور و همراهان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | سخنوری | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | نظم‌دهی اطلاعات | بیان نوشتاری | درک نوشتاری | وضوح گفتار | تشخیص گفتار | خلاقیت | ثبات دست و بازو | مهارت انگشتان | روانی ایده‌ها | استدلال قیاسی | تجسم | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | تشخیص رنگ بصری | دید دور | مهارت دستی | توجه انتخابی</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | وضوح گفتار | تشخیص گفتار | اصالت | ثبات دست و بازو | مهارت انگشتان | روانی ایده‌ها | استدلال قیاسی | تجسم | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | تشخیص رنگ بصری | بینایی دور | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>معلمان معماری، پس از متوسطه | آرشیوچی‌ها | معلمان آموزش فنی/حرفه‌ای، پس از متوسطه | تکنسین‌های شیمی | تکنسین‌ها و فناوران مهندسی عمران | دانشمندان حفاظت | هنرمندان صنایع دستی | موزه‌داران | هنرمندان هنرهای زیبا، شامل نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان ردیف اول کارگران محوطه‌سازی، خدمات چمن و نگهداری زمین | سرپرستان ردیف اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | سرپرستان ردیف اول کارگران تولید و عملیات | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | نقاشان، ساختمانی و نگهداری | کارگران نقاشی، پوشش‌دهی و تزئین | طراحان صحنه و نمایشگاه</t>
+          <t>مدرسان معماری، پس از متوسطه | آرشیوچی‌ها | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | تکنسین‌های شیمی | تکنسین‌ها و کارشناسان مهندسی عمران | دانشمندان حفاظت | هنرمندان صنایع دستی | موزه‌داران | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و بهره‌برداری | تکنسین‌های جنگل و حفاظت | پرداخت‌کاران مبلمان | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | مورخان | کتابداران و متخصصان مجموعه‌های رسانه‌ای | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | طراحان صحنه و نمایشگاه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple iMovie | Autodesk AutoCAD | نرم‌افزار Blackboard | نرم‌افزار وبلاگ‌نویسی | CATNYP | برگه‌های سبک آبشاری CSS | CatchTheWeb | Classification Web | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | Drupal | Dynix Digital Library | Electronic Online Systems International EOS.Web | نرم‌افزار ایمیل | Ex Libris Group Aleph | Ex Libris Group Voyager | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | FileMaker Pro | نرم‌افزار Google Workspace | نرم‌افزار گرافیکی | HTTrack | زبان نشانه‌گذاری ابرمتن HTML | Infovision Amlib | Inmagic Genie | Inmagic TextWorks | Innovative Interfaces Millennium | JavaScript | Kelowna Software L4U | سیستم مدیریت یادگیری LMS | LexisNexis | MC2 Systems Auto Librarian | Macropool Web Research | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Onfolio | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | National Library of Medicine DOCLINE | National Library of Medicine Medline | پایگاه‌های داده Online Computer Library Center (OCLC) | پایگاه‌های داده آنلاین | Oracle Java | PHP | PrimaSoft PC Small Library Organizer Pro | QuarkXPress | RCL Software Media Library Manager | Really Simple Syndication RSS | Saora Keepoint | SirsiDynix Symphony | SmugMug Flickr | نرم‌افزار شبکه‌های اجتماعی | Springshare LibGuides | زبان نشانه‌گذاری تعمیم‌یافته استاندارد SGML | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار سیستم مدیریت Surpass | Thomson Reuters Westlaw Edge | Thomson Scientific Dialog | نرم‌افزار مرورگر وب | WebClarity Software BookWhere | نرم‌افزار ویکی | WorldCat | Zoom | askSam Systems SurfSaver</t>
+          <t>Adobe Acrobat | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apple Final Cut Pro | Apple iMovie | Autodesk AutoCAD | نرم‌افزار Blackboard | نرم‌افزار وبلاگ‌نویسی | CATNYP | برگه‌های سبک آبشاری CSS | CatchTheWeb | Classification Web | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | Drupal | Dynix Digital Library | Electronic Online Systems International EOS.Web | نرم‌افزار ایمیل | Ex Libris Group Aleph | Ex Libris Group Voyager | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | FileMaker Pro | نرم‌افزار Google Workspace | نرم‌افزار گرافیکی | HTTrack | زبان نشانه‌گذاری ابرمتن HTML | Infovision Amlib | Inmagic Genie | Inmagic TextWorks | Innovative Interfaces Millennium | JavaScript | Kelowna Software L4U | سیستم مدیریت یادگیری LMS | LexisNexis | MC2 Systems Auto Librarian | Macropool Web Research | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Onfolio | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | National Library of Medicine DOCLINE | National Library of Medicine Medline | پایگاه‌های داده Online Computer Library Center (OCLC) | پایگاه‌های داده آنلاین | Oracle Java | PHP | PrimaSoft PC Small Library Organizer Pro | QuarkXPress | RCL Software Media Library Manager | Really Simple Syndication RSS | Saora Keepoint | SirsiDynix Symphony | SmugMug Flickr | نرم‌افزار شبکه‌های اجتماعی | Springshare LibGuides | زبان نشانه‌گذاری تعمیم‌یافته استاندارد SGML | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار سیستم مدیریت Surpass | Thomson Reuters Westlaw Edge | Thomson Scientific Dialog | نرم‌افزار مرورگر وب | WebClarity Software BookWhere | نرم‌افزار Wiki | WorldCat | Zoom | askSam Systems SurfSaver</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخنوری | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | بیان نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | آرشیوچی‌ها | معلمان علوم رایانه، پس از متوسطه | متخصصان پشتیبانی کاربر رایانه | موزه‌داران | مدیران پایگاه داده | متخصصان مدیریت اسناد | مدیران آموزشی، پس از متوسطه | معلمان آموزش، پس از متوسطه | کارمندان بایگانی | هماهنگ‌کنندگان آموزشی | دستیاران کتابخانه، دفتری | معلمان علوم کتابداری، پس از متوسطه | تکنسین‌های کتابخانه | تحلیلگران مدیریت | مدیران برنامه‌نویسی رسانه | کارمندان اداری، عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | مدیران وب</t>
+          <t>مدیران خدمات اداری | آرشیوچی‌ها | اساتید علوم رایانه، پس از متوسطه | متخصصان پشتیبانی کاربران کامپیوتر | موزه‌داران | مدیران پایگاه داده | متخصصان مدیریت اسناد | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | کارمندان بایگانی | هماهنگ‌کنندگان آموزشی | دستیاران کتابخانه، دفتری | مدرسان علوم کتابداری، آموزش عالی | تکنسین‌های کتابخانه | تحلیل‌گران مدیریت | مدیران برنامه‌ریزی رسانه | کارمندان دفتری عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | مدیران وب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بیان نوشتاری | دید دور | نظم‌دهی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار کارهای مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا صحیح بودن | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>آرشیوچی‌ها | معلمان علوم رایانه، پس از متوسطه | متخصصان پشتیبانی کاربر رایانه | مدیران پایگاه داده | متخصصان مدیریت اسناد | کارمندان بایگانی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | معلمان علوم کتابداری، پس از متوسطه | تحلیلگران مدیریت | کارمندان اداری، عمومی | اپراتورهای ماشین اداری، به جز رایانه | نمونه‌خوان‌ها و علامت‌گذاران کپی | پذیرش‌گران و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | دستیاران آماری | انبارداران و پرکننده سفارشات | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی</t>
+          <t>آرشیوچی‌ها | اساتید علوم رایانه، پس از متوسطه | متخصصان پشتیبانی کاربران کامپیوتر | مدیران پایگاه داده | متخصصان مدیریت اسناد | کارمندان بایگانی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، دفتری | مدرسان علوم کتابداری، آموزش عالی | تحلیل‌گران مدیریت | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | مصححان و نشانه‌گذاران کپی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | قفسه‌چین‌ها و پرکننده‌های سفارش | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنوری | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | وضوح گفتار | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | تشخیص گفتار | خلاقیت | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | حافظه | دید نزدیک | اشتراک زمانی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | سرعت بستار | تسهیلات عددی | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | حفظ کردن | بینایی نزدیک | تقسیم توجه | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی | محیط داخلی، بدون کنترل محیطی | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | محیط داخلی، بدون کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | بازرسان کشاورزی | معلمان علوم کشاورزی، پس از متوسطه | معلمان کسب‌وکار، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | مدیران ارشد اجرایی | کارکنان بهداشت جامعه | دانشمندان حفاظت | کشاورزان، دامداران و سایر مدیران کشاورزی | سرپرستان ردیف اول کارگران کشاورزی، شیلات و جنگلداری | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | تحلیلگران مدیریت | مدیران مراتع | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | دانشمندان خاک و گیاه</t>
+          <t>مهندسان کشاورزی | بازرسان کشاورزی | مدرسان علوم کشاورزی، پس از متوسطه | اساتید کسب‌وکار، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدیران ارشد اجرایی | مددکاران سلامت جامعه | دانشمندان حفاظت | کشاورزان، دامداران و سایر مدیران کشاورزی | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | تحلیل‌گران مدیریت | مدیران مراتع | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0036_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0036_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | درک کتبی | دید نزدیک | مرتب‌سازی اطلاعات | استدلال قیاسی | ابتکار و اصالت | روان بودن ایده‌ها | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | درک کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال قیاسی | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و زبان انگلیسی به غیرفارسی‌زبانان | مدرسان هنر، نمایش و موسیقی در آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان پیش‌دبستانی و مهدکودک به‌استثنای آموزش استثنایی | معلمان دوره اول متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | مربیان مهدکودک به‌استثنای آموزش استثنایی | مدرسان علوم ورزشی و اوقات فراغت در آموزش عالی | معلمان دوره دوم متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و مهدکودک | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی مراکز پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | درک کتبی | بیان کتبی | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و زبان انگلیسی به غیرفارسی‌زبانان | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | مدیران و مسئولان آموزشی مدارس ابتدایی و متوسطه | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان مهدکودک و پیش‌دبستانی به‌استثنای آموزش استثنایی | معلمان دوره اول متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | مربیان مراکز پیش‌دبستانی به‌استثنای آموزش استثنایی | معلمان دوره دوم متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی مراکز پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان مدارس ابتدایی و متوسطه به‌استثنای آموزش استثنایی | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | راهبردهای یادگیری | سخن گفتن | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
+          <t>درک مطلب | راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | روان بودن ایده‌ها | استدلال قیاسی | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | روانی ایده‌ها | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و زبان انگلیسی به غیرفارسی‌زبانان | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | مدرسان علوم تربیتی در آموزش عالی | مشاوران و کارشناسان هدایت تحصیلی و شغلی | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | کارشناسان برنامه‌ریزی و تدوین متون درسی | مربیان مهدکودک به‌استثنای آموزش استثنایی | مدرسان علوم ریاضی در آموزش عالی | معلمان دوره اول متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | معلمان دوره دوم متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و مهدکودک | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی مراکز پیش‌دبستانی | معلمان آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان مدارس ابتدایی و متوسطه به‌استثنای آموزش استثنایی | کمک‌معلمان آموزش استثنایی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه‌ها | روان‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روان بودن ایده‌ها | ابتکار و اصالت | توجه انتخابی | اشتراک زمانی | تجسم فضایی | حافظه و به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان خصوصی و مدرسان تقویتی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و زبان انگلیسی به غیرفارسی‌زبانان | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی | مدیران آموزش و توسعه منابع انسانی | کارشناسان برنامه‌ریزی و تدوین متون درسی | سایر مدرسان آموزش عالی | معلمان دوره ابتدایی به‌استثنای آموزش استثنایی | معلمان دوره دوم متوسطه به‌استثنای آموزش استثنایی و فنی و حرفه‌ای | کارشناسان ترویج و آموزش کشاورزی و اقتصاد خانواده | کارشناسان آموزش سلامت | مشاوران و کارشناسان هدایت تحصیلی و شغلی | مربیان و استعدادیابان ورزشی | مدرسان علوم ورزشی و اوقات فراغت در آموزش عالی | مدیران آموزشی، سایر تخصص‌ها | سایر دستیاران آموزشی و کمک‌معلمان</t>
+          <t>مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان خصوصی و مدرسان تقویتی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی | مدیران آموزش و بهسازی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | سایر مدرسان در آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | کارشناسان ترویج و آموزش کشاورزی و اقتصاد خانواده | کارشناسان آموزش بهداشت و ارتقای سلامت | مشاوران تحصیلی، شغلی و هدایت استعدادها | مربیان و استعدادیابان ورزشی | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | مدیران آموزشی، سایر موارد | سایر کمک‌معلمان و دستیاران آموزشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری | آموزش و تدریس | حقوق و علوم حکومتی</t>
+          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | اداری | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | حساسیت به مسئله | روان بودن ایده‌ها</t>
+          <t>درک کتبی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | درک شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | متصدیان مکاتبات و دبیرخانه | موزه‌داران | تحلیل‌گران جرم‌یابی دیجیتال | کارشناسان مدیریت اسناد و مدارک | ویراستاران | متصدیان بایگانی و پرونده‌ها | کارشناسان فناوری اطلاعات سلامت و مسئولان ثبت مدارک پزشکی | تاریخ‌نگاران و پژوهشگران تاریخ | کارشناسان برنامه‌ریزی و تدوین متون درسی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران و متصدیان دفتری کتابخانه | مدرسان علوم کتابداری و اطلاع‌رسانی در آموزش عالی | تکنسین‌های کتابداری | تکنسین‌ها و کارشناسان مرمت موزه | متصدیان امور دفتری و اداری عمومی | نمونه‌خوانان و غلط‌گیران متون | مسئولان دفاتر و منشی‌ها به‌استثنای حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | دستیاران آمار و تحلیل داده‌ها</t>
+          <t>انسان‌شناسان و باستان‌شناسان | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | موزه‌داران | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | کارشناسان مدیریت اسناد و مدارک | ویراستاران | متصدیان بایگانی و اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مورخان | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کتابداری | تکنسین‌ها و مرمت‌گران موزه | متصدیان امور دفتری و امور عمومی اداری | ویراستاران فنی و نمونه‌خوان‌ها | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | تاریخ و باستان‌شناسی | هنرهای تجسمی | مدیریت و امور اداری | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه‌ها | امور اداری و دفتری | آموزش و تدریس | جغرافیا | خدمات مشتریان و خدمات فردی | فلسفه و الهیات</t>
+          <t>زبان انگلیسی | تاریخ و باستان‌شناسی | هنرهای زیبا | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | اداری | آموزش و پرورش | جغرافیا | خدمات مشتری و شخصی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | دید نزدیک | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | ابتکار و اصالت | مرتب‌سازی اطلاعات | روان بودن ایده‌ها | تجسم فضایی | دید دور | توجه انتخابی | انعطاف‌پذیری تصویرسازی | تفکیک و تشخیص رنگ‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | اصالت | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تجسم | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | مدرسان انسان‌شناسی و باستان‌شناسی در آموزش عالی | مدرسان معماری در آموزش عالی | کارشناسان اسناد و آرشیو | مدرسان مطالعات منطقه‌ای، قومیتی و فرهنگی در آموزش عالی | مدیران هنری | مدرسان هنر، نمایش و موسیقی در آموزش عالی | مدرسان زبان و ادبیات انگلیسی در آموزش عالی | مدرسان جغرافیا در آموزش عالی | تاریخ‌نگاران و پژوهشگران تاریخ | مدرسان تاریخ در آموزش عالی | کارشناسان برنامه‌ریزی و تدوین متون درسی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران و متصدیان دفتری کتابخانه | مدرسان علوم کتابداری و اطلاع‌رسانی در آموزش عالی | تکنسین‌های کتابداری | تکنسین‌ها و کارشناسان مرمت موزه | طراحان صحنه و غرفه‌های نمایشگاهی | دستیاران پژوهشی علوم اجتماعی | راهنمایان تور و همراهان گردشگری</t>
+          <t>انسان‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان اسناد و آرشیو | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدیران هنری | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مورخان | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کتابداری | تکنسین‌ها و مرمت‌گران موزه | طراحان صحنه و نمایشگاه | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | راهنمایان تور و گردشگری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>هنرهای تجسمی | زبان انگلیسی | ایمنی و امنیت عمومی | تاریخ و باستان‌شناسی | مدیریت و امور اداری | شیمی</t>
+          <t>هنرهای زیبا | زبان انگلیسی | ایمنی و امنیت عمومی | تاریخ و باستان‌شناسی | مدیریت و اداره | شیمی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی | وضوح گفتار | تشخیص گفتار | ابتکار و اصالت | پایداری دست و بازو | چابکی انگشتان | روان بودن ایده‌ها | استدلال قیاسی | تجسم فضایی | حساسیت به مسئله | انعطاف‌پذیری تصویرسازی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | تفکیک و تشخیص رنگ‌ها | دید دور | چابکی دستی | توجه انتخابی</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | وضوح گفتار | تشخیص گفتار | اصالت | ثبات دست و بازو | مهارت انگشتان | روانی ایده‌ها | استدلال قیاسی | تجسم | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | تشخیص رنگ بصری | بینایی دور | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدرسان معماری در آموزش عالی | کارشناسان اسناد و آرشیو | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | تکنسین‌های شیمی | تکنسین‌های مهندسی عمران | کارشناسان علوم حفاظت و زیست‌محیطی | هنرمندان صنایع دستی | موزه‌داران | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان کارگران فضای سبز، باغبانی و محوطه‌سازی | سرپرستان مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان کارگران خطوط تولید و بهره‌برداری | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | رنگ‌کاران و رویه‌کوبان مصنوعات چوبی | تکنسین‌های زمین‌شناسی به‌استثنای هیدرولوژی | تاریخ‌نگاران و پژوهشگران تاریخ | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | طراحان صحنه و غرفه‌های نمایشگاهی</t>
+          <t>استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان اسناد و آرشیو | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | تکنسین‌های شیمی | کارشناسان و تکنسین‌های مهندسی عمران | دانشمندان حفاظت از منابع طبیعی | هنرمندان صنایع دستی | موزه‌داران | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران تولید و عملیات | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | مورخان | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | طراحان صحنه و نمایشگاه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | امور اداری و دفتری | ارتباطات و رسانه‌ها | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | اداری | ارتباطات و رسانه | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | حساسیت به مسئله | روان بودن ایده‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان اسناد و آرشیو | مدرسان علوم رایانه در آموزش عالی | کارشناسان پشتیبانی و خدمات کاربران رایانه | موزه‌داران | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | مدیران آموزشی در آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | متصدیان بایگانی و پرونده‌ها | کارشناسان برنامه‌ریزی و تدوین متون درسی | کمک‌کتابداران و متصدیان دفتری کتابخانه | مدرسان علوم کتابداری و اطلاع‌رسانی در آموزش عالی | تکنسین‌های کتابداری | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | مدیران برنامه‌ریزی و تامین رسانه | متصدیان امور دفتری و اداری عمومی | مسئولان دفاتر و منشی‌ها به‌استثنای حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | مدیران و کارشناسان پشتیبانی وب‌سایت</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان اسناد و آرشیو | استادان علوم رایانه، آموزش عالی | متخصصان پشتیبانی کاربران رایانه | موزه‌داران | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | متصدیان بایگانی و اسناد | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کمک‌کتابداران دفتری | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کتابداری | کارشناسان تحلیل مدیریت و روش‌ها | مدیران برنامه‌ریزی و پخش رسانه | متصدیان امور دفتری و امور عمومی اداری | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | مدیران وب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | راهبردهای یادگیری | تفکر انتقادی</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | دید دور | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بینایی دور | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان اسناد و آرشیو | مدرسان علوم رایانه در آموزش عالی | کارشناسان پشتیبانی و خدمات کاربران رایانه | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و پرونده‌ها | کارشناسان برنامه‌ریزی و تدوین متون درسی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران و متصدیان دفتری کتابخانه | مدرسان علوم کتابداری و اطلاع‌رسانی در آموزش عالی | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | متصدیان امور دفتری و اداری عمومی | اپراتورهای ماشین‌های اداری به‌استثنای رایانه | نمونه‌خوانان و غلط‌گیران متون | متصدیان پذیرش و اطلاع‌رسانی | مسئولان دفاتر و منشی‌ها به‌استثنای حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | دستیاران آمار و تحلیل داده‌ها | کارگران چیدمان و آماده‌سازی سفارش‌ها | کمک‌معلمان مدارس ابتدایی و متوسطه به‌استثنای آموزش استثنایی</t>
+          <t>کارشناسان اسناد و آرشیو | استادان علوم رایانه، آموزش عالی | متخصصان پشتیبانی کاربران رایانه | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | ویراستاران فنی و نمونه‌خوان‌ها | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | متصدیان چیدمان و آماده‌سازی سفارش | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | تولید محصولات کشاورزی و دامی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | ارتباطات و رسانه‌ها | مدیریت و امور اداری | رایانه و الکترونیک | امور اداری و دفتری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | تولید مواد غذایی | خدمات مشتری و شخصی | زیست‌شناسی | ارتباطات و رسانه | مدیریت و اداره | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | تشخیص گفتار | ابتکار و اصالت | انعطاف‌پذیری طبقه‌بندی | روان بودن ایده‌ها | حافظه و به‌خاطرسپاری | دید نزدیک | اشتراک زمانی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری تصویرسازی | سرعت تشخیص الگو | سهولت در کار با اعداد | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | حفظ کردن | بینایی نزدیک | تقسیم توجه | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | مدرسان علوم کشاورزی در آموزش عالی | مدرسان مدیریت و بازرگانی در آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | مدیران ارشد اجرایی | رابطان و مروجان سلامت جامعه | کارشناسان علوم حفاظت و زیست‌محیطی | مدیران تولید کشاورزی، دامپروری و شیلات | سرپرستان کارگران کشاورزی، شیلات و جنگل‌داری | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان و مهندسان جنگل‌داری | کارشناسان آموزش سلامت | کارشناسان برنامه‌ریزی و تدوین متون درسی | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | کارشناسان و مدیران مرتع‌داری | کارشناسان فروش خدمات به‌استثنای تبلیغات، بیمه، خدمات مالی و گردشگری | کارشناسان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم اداری و مدیریت، آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدیران عامل و مدیران ارشد اجرایی | رابطان سلامت و بهورزان | دانشمندان حفاظت از منابع طبیعی | مدیران امور کشاورزی، دامپروری و شیلات | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران و کارشناسان مدیریت مراتع | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
